--- a/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>22.901</v>
+        <v>21.398</v>
       </c>
       <c r="B2">
-        <v>22.556</v>
+        <v>21.037</v>
       </c>
       <c r="C2">
-        <v>23.26</v>
+        <v>21.762</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>23.543</v>
+        <v>22.314</v>
       </c>
       <c r="B2">
-        <v>23.194</v>
+        <v>21.962</v>
       </c>
       <c r="C2">
-        <v>23.889</v>
+        <v>22.664</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>28.175</v>
+        <v>26.182</v>
       </c>
       <c r="B2">
-        <v>27.771</v>
+        <v>25.755</v>
       </c>
       <c r="C2">
-        <v>28.582</v>
+        <v>26.636</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>28.483</v>
+        <v>27.038</v>
       </c>
       <c r="B2">
-        <v>28.059</v>
+        <v>26.593</v>
       </c>
       <c r="C2">
-        <v>28.875</v>
+        <v>27.484</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>21.398</v>
+        <v>23.483</v>
       </c>
       <c r="B2">
-        <v>21.037</v>
+        <v>23.166</v>
       </c>
       <c r="C2">
-        <v>21.762</v>
+        <v>23.806</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>22.314</v>
+        <v>24.137</v>
       </c>
       <c r="B2">
-        <v>21.962</v>
+        <v>23.814</v>
       </c>
       <c r="C2">
-        <v>22.664</v>
+        <v>24.456</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>26.182</v>
+        <v>30.652</v>
       </c>
       <c r="B2">
-        <v>25.755</v>
+        <v>30.238</v>
       </c>
       <c r="C2">
-        <v>26.636</v>
+        <v>31.074</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>27.038</v>
+        <v>30.971</v>
       </c>
       <c r="B2">
-        <v>26.593</v>
+        <v>30.54</v>
       </c>
       <c r="C2">
-        <v>27.484</v>
+        <v>31.392</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A18C0CC3B02F8FE922E27E5D22120966FFFA5BA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unadj_boot_all_summary_stats" sheetId="1" r:id="rId1"/>
@@ -12,13 +18,54 @@
     <sheet name="adj_boot_all_summary_stats" sheetId="3" r:id="rId3"/>
     <sheet name="adj_boot_user_summary_stats" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>mean_boot_visits_all</t>
+  </si>
+  <si>
+    <t>lower_ci_boot_visits_all</t>
+  </si>
+  <si>
+    <t>upper_ci_boot_visits_all</t>
+  </si>
+  <si>
+    <t>mean_boot_visits_user</t>
+  </si>
+  <si>
+    <t>lower_ci_boot_visits_user</t>
+  </si>
+  <si>
+    <t>upper_ci_boot_visits_user</t>
+  </si>
+  <si>
+    <t>mean_boot_visits_all_adj</t>
+  </si>
+  <si>
+    <t>lower_ci_boot_visits_all_adj</t>
+  </si>
+  <si>
+    <t>upper_ci_boot_visits_all_adj</t>
+  </si>
+  <si>
+    <t>mean_boot_visits_user_adj</t>
+  </si>
+  <si>
+    <t>lower_ci_boot_visits_user_adj</t>
+  </si>
+  <si>
+    <t>upper_ci_boot_visits_user_adj</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,13 +113,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -110,7 +165,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -144,6 +199,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -178,9 +234,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -353,36 +410,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mean_boot_visits_all</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lower_ci_boot_visits_all</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>upper_ci_boot_visits_all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>23.483</v>
+        <v>23.483000000000001</v>
       </c>
       <c r="B2">
         <v>23.166</v>
       </c>
       <c r="C2">
-        <v>23.806</v>
+        <v>23.806000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -391,28 +442,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mean_boot_visits_user</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lower_ci_boot_visits_user</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>upper_ci_boot_visits_user</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>24.137</v>
       </c>
@@ -429,36 +474,30 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mean_boot_visits_all_adj</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lower_ci_boot_visits_all_adj</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>upper_ci_boot_visits_all_adj</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>30.652</v>
+        <v>30.652000000000001</v>
       </c>
       <c r="B2">
         <v>30.238</v>
       </c>
       <c r="C2">
-        <v>31.074</v>
+        <v>31.074000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -467,28 +506,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mean_boot_visits_user_adj</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lower_ci_boot_visits_user_adj</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>upper_ci_boot_visits_user_adj</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>30.971</v>
       </c>
@@ -496,7 +529,7 @@
         <v>30.54</v>
       </c>
       <c r="C2">
-        <v>31.392</v>
+        <v>31.391999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
+++ b/OMOP Analysis/Results/Output_visits_OMOP-Boot.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_A18C0CC3B02F8FE922E27E5D22120966FFFA5BA6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="unadj_boot_all_summary_stats" sheetId="1" r:id="rId1"/>
@@ -18,54 +12,13 @@
     <sheet name="adj_boot_all_summary_stats" sheetId="3" r:id="rId3"/>
     <sheet name="adj_boot_user_summary_stats" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>mean_boot_visits_all</t>
-  </si>
-  <si>
-    <t>lower_ci_boot_visits_all</t>
-  </si>
-  <si>
-    <t>upper_ci_boot_visits_all</t>
-  </si>
-  <si>
-    <t>mean_boot_visits_user</t>
-  </si>
-  <si>
-    <t>lower_ci_boot_visits_user</t>
-  </si>
-  <si>
-    <t>upper_ci_boot_visits_user</t>
-  </si>
-  <si>
-    <t>mean_boot_visits_all_adj</t>
-  </si>
-  <si>
-    <t>lower_ci_boot_visits_all_adj</t>
-  </si>
-  <si>
-    <t>upper_ci_boot_visits_all_adj</t>
-  </si>
-  <si>
-    <t>mean_boot_visits_user_adj</t>
-  </si>
-  <si>
-    <t>lower_ci_boot_visits_user_adj</t>
-  </si>
-  <si>
-    <t>upper_ci_boot_visits_user_adj</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,21 +66,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +110,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,7 +144,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,10 +178,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,30 +353,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_boot_visits_all</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lower_ci_boot_visits_all</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>upper_ci_boot_visits_all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
-        <v>23.483000000000001</v>
+        <v>166.679</v>
       </c>
       <c r="B2">
-        <v>23.166</v>
+        <v>164.524</v>
       </c>
       <c r="C2">
-        <v>23.806000000000001</v>
+        <v>168.934</v>
       </c>
     </row>
   </sheetData>
@@ -442,30 +391,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_boot_visits_user</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lower_ci_boot_visits_user</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>upper_ci_boot_visits_user</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
-        <v>24.137</v>
+        <v>93.476</v>
       </c>
       <c r="B2">
-        <v>23.814</v>
+        <v>92.139</v>
       </c>
       <c r="C2">
-        <v>24.456</v>
+        <v>94.762</v>
       </c>
     </row>
   </sheetData>
@@ -474,30 +429,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_boot_visits_all_adj</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lower_ci_boot_visits_all_adj</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>upper_ci_boot_visits_all_adj</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
-        <v>30.652000000000001</v>
+        <v>213.648</v>
       </c>
       <c r="B2">
-        <v>30.238</v>
+        <v>210.717</v>
       </c>
       <c r="C2">
-        <v>31.074000000000002</v>
+        <v>216.64</v>
       </c>
     </row>
   </sheetData>
@@ -506,30 +467,36 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_boot_visits_user_adj</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lower_ci_boot_visits_user_adj</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>upper_ci_boot_visits_user_adj</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
-        <v>30.971</v>
+        <v>120.267</v>
       </c>
       <c r="B2">
-        <v>30.54</v>
+        <v>118.403</v>
       </c>
       <c r="C2">
-        <v>31.391999999999999</v>
+        <v>122.099</v>
       </c>
     </row>
   </sheetData>
